--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.95404866910561</v>
+        <v>1.455032908729662</v>
       </c>
       <c r="D2" t="n">
-        <v>8.588113374436935</v>
+        <v>1.395568423346002</v>
       </c>
       <c r="E2" t="n">
-        <v>26.47356042025748</v>
+        <v>4.30195356829184</v>
       </c>
       <c r="F2" t="n">
-        <v>23.77997956899889</v>
+        <v>3.86424667996232</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.69382613214793</v>
+        <v>8.88774674647404</v>
       </c>
       <c r="D3" t="n">
-        <v>54.52283985254903</v>
+        <v>8.859961476039217</v>
       </c>
       <c r="E3" t="n">
-        <v>26.47356042025748</v>
+        <v>4.30195356829184</v>
       </c>
       <c r="F3" t="n">
-        <v>23.77997956899889</v>
+        <v>3.86424667996232</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.63256553808121</v>
+        <v>11.6402918999382</v>
       </c>
       <c r="D4" t="n">
-        <v>62.57473039070032</v>
+        <v>10.1683936884888</v>
       </c>
       <c r="E4" t="n">
-        <v>26.47356042025748</v>
+        <v>4.30195356829184</v>
       </c>
       <c r="F4" t="n">
-        <v>23.77997956899889</v>
+        <v>3.86424667996232</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
